--- a/新建 Microsoft Excel 工作表.xlsx
+++ b/新建 Microsoft Excel 工作表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workFile\演示文件\demo-warehouse\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC7AB9-6A15-4475-A9EB-B426D8151D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,13 +25,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +66,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +343,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/新建 Microsoft Excel 工作表.xlsx
+++ b/新建 Microsoft Excel 工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workFile\演示文件\demo-warehouse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DC7AB9-6A15-4475-A9EB-B426D8151D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146BD101-32F9-4CC7-AD7A-9465F46C605A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,7 +364,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">

--- a/新建 Microsoft Excel 工作表.xlsx
+++ b/新建 Microsoft Excel 工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workFile\演示文件\demo-warehouse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146BD101-32F9-4CC7-AD7A-9465F46C605A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713208CC-45C8-4606-B8BD-77D167C008D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,97 +344,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
